--- a/data/externalStats/File1/RPT_RPT8255149037738UH_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT8255149037738UH_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>40294.15219393585</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>34.07302870312816</v>
+        <v>34.07302870312817</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2178,26 +2178,26 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>5520.587381943594</v>
+        <v>5520.587381943595</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>9.11370690115573</v>
+        <v>9.113706901155732</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>ZEPBOUND</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>0.8344372529285075</v>
+        <v>15.58715639929586</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>ELIQUIS</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>ORAL ANTICOAGULANTS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AN27" s="58" t="n">
@@ -2342,16 +2342,16 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>0</v>
+        <v>0.8344372529285075</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -2419,16 +2419,16 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>ZEPBOUND</t>
+          <t>ACIPHEX</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>GLP-1 ANTI-OBESITY AGENTS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>15.58715639929586</v>
+        <v>3.985337375390821</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -2496,16 +2496,16 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>LIPITOR</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>STATINS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>0</v>
+        <v>9.125763151565664</v>
       </c>
     </row>
     <row r="31">
@@ -2559,16 +2559,16 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>JARDIANCE</t>
+          <t>AVODART</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+          <t>PROSTATIC HYPERTROPHY AGENTS</t>
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>0</v>
+        <v>2.017150935141111</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>XARELTO</t>
+          <t>SYNTHROID</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>ORAL ANTICOAGULANTS</t>
+          <t>THYROID HORMONES</t>
         </is>
       </c>
       <c r="AN32" s="58" t="n">
@@ -2707,16 +2707,16 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>ACIPHEX</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="AN33" s="58" t="n">
-        <v>3.985337375390821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2765,35 +2765,35 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>TRELEGY ELLIPTA</t>
+          <t>VYZULTA</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>OPHTHALMIC PROSTAGLANDINS</t>
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>575.7834605077868</v>
+        <v>2155.872589308654</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>1.930407561055622</v>
+        <v>4.919003304368093</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>LIPITOR</t>
+          <t>NEXIUM</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>STATINS &amp; COMBOS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>9.125763151565664</v>
+        <v>4.981671719238526</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -2842,35 +2842,35 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>VYZULTA</t>
+          <t>MYRBETRIQ</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>OPHTHALMIC PROSTAGLANDINS</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2155.872589308654</v>
+        <v>1917.337989665621</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>4.919003304368093</v>
+        <v>4.522238241588476</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>AVODART</t>
+          <t>VIAGRA</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>PROSTATIC HYPERTROPHY AGENTS</t>
+          <t>IMPOTENCE AGENTS</t>
         </is>
       </c>
       <c r="AN35" s="58" t="n">
-        <v>2.017150935141111</v>
+        <v>8.685861698479103</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -2919,35 +2919,35 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>OZEMPIC</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>538.8970938079664</v>
+        <v>1595.870947226147</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>1.807924278332933</v>
+        <v>1.064062481716026</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>SYNTHROID</t>
+          <t>RASUVO</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>THYROID HORMONES</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>0</v>
+        <v>13.03311468417755</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -2996,31 +2996,31 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>MYRBETRIQ</t>
+          <t>TRINTELLIX</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>ANTIDEPRESSANTS</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>1917.337989665621</v>
+        <v>1561.053741299694</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>4.522238241588476</v>
+        <v>7.487248693337843</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>DEXCOM G7 SENSOR</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AN37" s="58" t="n">
@@ -3073,35 +3073,35 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>ARNUITY ELLIPTA</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>INHALED CORTICOSTEROIDS (ICS)</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>1595.870947226147</v>
+        <v>1398.84733354894</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>1.064062481716026</v>
+        <v>3.641723707785178</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>NEXIUM</t>
+          <t>MIEBO</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>OPHTHALMICS - MISC.</t>
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>4.981671719238526</v>
+        <v>7.288591773944473</v>
       </c>
     </row>
     <row r="39">
@@ -3136,35 +3136,35 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>TRINTELLIX</t>
+          <t>V-GO 20</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>ANTIDEPRESSANTS</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1561.053741299694</v>
+        <v>1288.621227289372</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>7.487248693337843</v>
+        <v>0</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>VIAGRA</t>
+          <t>INDERAL LA</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>IMPOTENCE AGENTS</t>
+          <t>BETA BLOCKERS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN39" s="58" t="n">
-        <v>8.685861698479103</v>
+        <v>0.957711257455976</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -3203,35 +3203,35 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ARNUITY ELLIPTA</t>
+          <t>V-GO 30</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>INHALED CORTICOSTEROIDS (ICS)</t>
+          <t>INSULIN ADMINISTRATION SUPPLIES</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1398.84733354894</v>
+        <v>1288.621227289372</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>3.641723707785178</v>
+        <v>0</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>RASUVO</t>
+          <t>XDEMVY</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>OPHTHALMIC ANTI-INFECTIVES</t>
         </is>
       </c>
       <c r="AN40" s="58" t="n">
-        <v>13.03311468417755</v>
+        <v>2.411334708752383</v>
       </c>
     </row>
     <row r="41">
@@ -3280,35 +3280,35 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>V-GO 20</t>
+          <t>PREMARIN</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>VAGINAL ESTROGENS</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1288.621227289372</v>
+        <v>914.0056870913653</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>0</v>
+        <v>4.931725028513852</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>DEXCOM G7 SENSOR</t>
+          <t>QNASL</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+          <t>NASAL STEROIDS</t>
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>0</v>
+        <v>4.817242379133649</v>
       </c>
     </row>
     <row r="42">
@@ -3357,35 +3357,35 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>V-GO 30</t>
+          <t>PAXLOVID</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>INSULIN ADMINISTRATION SUPPLIES</t>
+          <t>MISC. ANTIVIRALS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1288.621227289372</v>
+        <v>798.6816040404954</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>0</v>
+        <v>1.996222777286802</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>MIEBO</t>
+          <t>LEXAPRO</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - MISC.</t>
+          <t>ANTIDEPRESSANTS</t>
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>7.288591773944473</v>
+        <v>3.073709385991972</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>PREMARIN</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>VAGINAL ESTROGENS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>914.0056870913653</v>
+        <v>740.9626946296806</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>4.931725028513852</v>
+        <v>2.170745535797251</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>INDERAL LA</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>BETA BLOCKERS &amp; COMBOS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>0.957711257455976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>PAXLOVID</t>
+          <t>TRELEGY ELLIPTA</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>MISC. ANTIVIRALS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>798.6816040404954</v>
+        <v>575.7834605077868</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>1.996222777286802</v>
+        <v>1.930407561055622</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
       </c>
       <c r="AL44" s="86" t="inlineStr">
         <is>
-          <t>XDEMVY</t>
+          <t>VALTREX</t>
         </is>
       </c>
       <c r="AM44" s="86" t="inlineStr">
         <is>
-          <t>OPHTHALMIC ANTI-INFECTIVES</t>
+          <t>HERPES AGENTS</t>
         </is>
       </c>
       <c r="AN44" s="87" t="n">
-        <v>2.411334708752383</v>
+        <v>5.870367186174204</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" thickBot="1">
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
@@ -4715,19 +4715,19 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>26.65588284009955</v>
+        <v>26.65588284009954</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>32.74194938540774</v>
+        <v>32.74194938540771</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -4736,13 +4736,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98398526604897</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.10887888966493</v>
+        <v>32.10887888966494</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.557552449006991</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>IRRITABLE BOWEL SYNDROME (IBS) AGENTS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>193.4160942446357</v>
+        <v>740.9626946296806</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>1.126630091462136</v>
+        <v>2.170745535797251</v>
       </c>
     </row>
     <row r="64">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>IRRITABLE BOWEL SYNDROME (IBS) AGENTS</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>740.9626946296806</v>
+        <v>193.4160942446356</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>2.170745535797251</v>
+        <v>1.126630091462136</v>
       </c>
     </row>
     <row r="65">
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>47.60579870684875</v>
@@ -4931,14 +4931,14 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>ATYPICAL ANTIPSYCHOTICS</t>
+          <t>LAXATIVES</t>
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>45.95450054462142</v>
+        <v>146.6279233888765</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>0.2875491833404485</v>
+        <v>2.42741624254244</v>
       </c>
     </row>
     <row r="66">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>LAXATIVES</t>
+          <t>RAPID ACTING</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>146.6279233888765</v>
+        <v>83.1208440483243</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>2.42741624254244</v>
+        <v>4.540520310945614</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -5094,14 +5094,14 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>RAPID ACTING</t>
+          <t>ATYPICAL ANTIPSYCHOTICS</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>83.1208440483243</v>
+        <v>45.95450054462142</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>4.540520310945614</v>
+        <v>0.2875491833404485</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5153,7 +5153,7 @@
         <v>28.11758592367504</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>284.2684910567109</v>
+        <v>284.2684910567108</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>39.62531155453372</v>
@@ -6387,7 +6387,7 @@
         <v>13.44783519037637</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>23.9222183650781</v>
+        <v>23.92221836507809</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
@@ -7211,19 +7211,19 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.03665471204857</v>
+        <v>32.03665471204856</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>38.12272125735676</v>
+        <v>38.12272125735673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -7232,13 +7232,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.89417964245902</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.01907326607498</v>
+        <v>39.019073266075</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>0.557552449006991</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>47.60579870684875</v>
@@ -8712,16 +8712,16 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>ZEPBOUND</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>0</v>
+        <v>19.48394549911982</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>5758.61418938181</v>
+        <v>5758.614189381809</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>9.141959392549317</v>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AN27" s="58" t="n">
@@ -8866,16 +8866,16 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>ELIQUIS</t>
+          <t>ACIPHEX</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>ORAL ANTICOAGULANTS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>0</v>
+        <v>3.969595292758027</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>ZEPBOUND</t>
+          <t>LIPITOR</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>GLP-1 ANTI-OBESITY AGENTS</t>
+          <t>STATINS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>19.48394549911982</v>
+        <v>9.174859757321087</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -9020,16 +9020,16 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>AVODART</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>PROSTATIC HYPERTROPHY AGENTS</t>
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>0</v>
+        <v>2.023444446058751</v>
       </c>
     </row>
     <row r="31">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>JARDIANCE</t>
+          <t>SYNTHROID</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+          <t>THYROID HORMONES</t>
         </is>
       </c>
       <c r="AN31" s="58" t="n">
@@ -9154,16 +9154,16 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>ACIPHEX</t>
+          <t>VIAGRA</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>IMPOTENCE AGENTS</t>
         </is>
       </c>
       <c r="AN32" s="58" t="n">
-        <v>3.969595292758027</v>
+        <v>9.026955487378377</v>
       </c>
     </row>
     <row r="33">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>2317.491710986315</v>
+        <v>2317.491710986316</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>4.864353177656564</v>
@@ -9231,12 +9231,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>TRELEGY ELLIPTA</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="AN33" s="58" t="n">
@@ -9308,16 +9308,16 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>OZEMPIC</t>
+          <t>RASUVO</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>0</v>
+        <v>13.39308931175454</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -9385,16 +9385,16 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>LIPITOR</t>
+          <t>NEXIUM</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>STATINS &amp; COMBOS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN35" s="58" t="n">
-        <v>9.174859757321087</v>
+        <v>4.961994115947533</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -9462,16 +9462,16 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>AVODART</t>
+          <t>DEXCOM G7 SENSOR</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>PROSTATIC HYPERTROPHY AGENTS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>2.023444446058751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -9539,16 +9539,16 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>SYNTHROID</t>
+          <t>MIEBO</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>THYROID HORMONES</t>
+          <t>OPHTHALMICS - MISC.</t>
         </is>
       </c>
       <c r="AN37" s="58" t="n">
-        <v>0</v>
+        <v>6.797705117969311</v>
       </c>
     </row>
     <row r="38" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -9616,16 +9616,16 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>VIAGRA</t>
+          <t>INDERAL LA</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>IMPOTENCE AGENTS</t>
+          <t>BETA BLOCKERS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>9.026955487378377</v>
+        <v>0.9357509383225104</v>
       </c>
     </row>
     <row r="39">
@@ -9679,16 +9679,16 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>XDEMVY</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>OPHTHALMIC ANTI-INFECTIVES</t>
         </is>
       </c>
       <c r="AN39" s="58" t="n">
-        <v>0</v>
+        <v>2.592208925255899</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -9746,16 +9746,16 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>RASUVO</t>
+          <t>LEXAPRO</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>ANTIDEPRESSANTS</t>
         </is>
       </c>
       <c r="AN40" s="58" t="n">
-        <v>13.39308931175454</v>
+        <v>3.114743406294965</v>
       </c>
     </row>
     <row r="41">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>NEXIUM</t>
+          <t>QNASL</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>NASAL STEROIDS</t>
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>4.961994115947533</v>
+        <v>4.668437762042212</v>
       </c>
     </row>
     <row r="42">
@@ -9900,16 +9900,16 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>DEXCOM G7 SENSOR</t>
+          <t>COZAAR</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+          <t>ANGIOTENSIN II RECEPTOR ANTAGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>0</v>
+        <v>5.627518735115959</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -9977,16 +9977,16 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>LINZESS</t>
+          <t>CEQUA</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>IRRITABLE BOWEL SYNDROME (IBS) AGENTS</t>
+          <t>OPHTHALMIC IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>0</v>
+        <v>1.99057346682708</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -10054,16 +10054,16 @@
       </c>
       <c r="AL44" s="86" t="inlineStr">
         <is>
-          <t>MIEBO</t>
+          <t>VALTREX</t>
         </is>
       </c>
       <c r="AM44" s="86" t="inlineStr">
         <is>
-          <t>OPHTHALMICS - MISC.</t>
+          <t>HERPES AGENTS</t>
         </is>
       </c>
       <c r="AN44" s="87" t="n">
-        <v>6.797705117969311</v>
+        <v>5.790177970411064</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" thickBot="1">
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2317.491710986315</v>
+        <v>2317.491710986316</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>10.72860902967588</v>
@@ -10870,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
@@ -11239,19 +11239,19 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>26.65588284009955</v>
+        <v>26.65588284009954</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>32.74194938540774</v>
+        <v>32.74194938540771</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -11260,13 +11260,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98398526604897</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.10887888966493</v>
+        <v>32.10887888966494</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.557552449006991</v>
@@ -11406,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>47.60579870684875</v>
@@ -11609,14 +11609,14 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
         <v>0</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>0</v>
+        <v>19.48394549911982</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -11668,7 +11668,7 @@
         <v>28.11758592367504</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>284.2684910567109</v>
+        <v>284.2684910567108</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>39.62531155453372</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>ORAL ANTICOAGULANTS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
@@ -12902,7 +12902,7 @@
         <v>13.44783519037637</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>23.9222183650781</v>
+        <v>23.92221836507809</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -13695,7 +13695,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
@@ -13726,19 +13726,19 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.03665471204857</v>
+        <v>32.03665471204856</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>38.12272125735676</v>
+        <v>38.12272125735673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -13747,13 +13747,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.89417964245902</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.01907326607498</v>
+        <v>39.019073266075</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>0.557552449006991</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -13865,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>47.60579870684875</v>
@@ -15227,16 +15227,16 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>ZEPBOUND</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>0</v>
+        <v>23.38073459894379</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -15297,19 +15297,19 @@
         <v>6048.064903563136</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>9.146347533057739</v>
+        <v>9.146347533057741</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AN27" s="58" t="n">
@@ -15381,16 +15381,16 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>ZEPBOUND</t>
+          <t>ACIPHEX</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>GLP-1 ANTI-OBESITY AGENTS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>23.38073459894379</v>
+        <v>3.945658633142696</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -15458,16 +15458,16 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>LIPITOR</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>STATINS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>0</v>
+        <v>9.20752225805715</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -15535,16 +15535,16 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>JARDIANCE</t>
+          <t>AVODART</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+          <t>PROSTATIC HYPERTROPHY AGENTS</t>
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>0</v>
+        <v>2.0264998471723</v>
       </c>
     </row>
     <row r="31">
@@ -15598,16 +15598,16 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>ACIPHEX</t>
+          <t>SYNTHROID</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>THYROID HORMONES</t>
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>3.945658633142696</v>
+        <v>0</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -15669,16 +15669,16 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>TRELEGY ELLIPTA</t>
+          <t>VIAGRA</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMPOTENCE AGENTS</t>
         </is>
       </c>
       <c r="AN32" s="58" t="n">
-        <v>0</v>
+        <v>9.359508527533396</v>
       </c>
     </row>
     <row r="33">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>OZEMPIC</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="AN33" s="58" t="n">
@@ -15823,16 +15823,16 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>LIPITOR</t>
+          <t>NEXIUM</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>STATINS &amp; COMBOS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>9.20752225805715</v>
+        <v>4.93207329142837</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -15900,16 +15900,16 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>AVODART</t>
+          <t>DEXCOM G7 SENSOR</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>PROSTATIC HYPERTROPHY AGENTS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AN35" s="58" t="n">
-        <v>2.0264998471723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -15977,16 +15977,16 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>SYNTHROID</t>
+          <t>RASUVO</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>THYROID HORMONES</t>
+          <t>CHRONIC INFLAMMATORY DISEASE</t>
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>0</v>
+        <v>10.38270607772277</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -16054,16 +16054,16 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>ELIQUIS</t>
+          <t>XDEMVY</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>ORAL ANTICOAGULANTS</t>
+          <t>OPHTHALMIC ANTI-INFECTIVES</t>
         </is>
       </c>
       <c r="AN37" s="58" t="n">
-        <v>0</v>
+        <v>2.753936840102614</v>
       </c>
     </row>
     <row r="38" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>904.0980860287003</v>
+        <v>904.0980860287001</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2.294824335148659</v>
@@ -16131,16 +16131,16 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>VIAGRA</t>
+          <t>INDERAL LA</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>IMPOTENCE AGENTS</t>
+          <t>BETA BLOCKERS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>9.359508527533396</v>
+        <v>0.9126191751271781</v>
       </c>
     </row>
     <row r="39">
@@ -16194,16 +16194,16 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>MIEBO</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>OPHTHALMICS - MISC.</t>
         </is>
       </c>
       <c r="AN39" s="58" t="n">
-        <v>0</v>
+        <v>6.259258895574963</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -16251,7 +16251,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>624.394924220298</v>
+        <v>624.3949242202979</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>1.947948910730224</v>
@@ -16261,16 +16261,16 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>NEXIUM</t>
+          <t>LEXAPRO</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>ANTIDEPRESSANTS</t>
         </is>
       </c>
       <c r="AN40" s="58" t="n">
-        <v>4.93207329142837</v>
+        <v>3.15483015393398</v>
       </c>
     </row>
     <row r="41">
@@ -16338,16 +16338,16 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>DEXCOM G7 SENSOR</t>
+          <t>QNASL</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+          <t>NASAL STEROIDS</t>
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>0</v>
+        <v>4.490616967686024</v>
       </c>
     </row>
     <row r="42">
@@ -16415,16 +16415,16 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>RASUVO</t>
+          <t>COZAAR</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>CHRONIC INFLAMMATORY DISEASE</t>
+          <t>ANGIOTENSIN II RECEPTOR ANTAGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>10.38270607772277</v>
+        <v>5.806980307578807</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -16492,16 +16492,16 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>XDEMVY</t>
+          <t>CEQUA</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>OPHTHALMIC ANTI-INFECTIVES</t>
+          <t>OPHTHALMIC IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>2.753936840102614</v>
+        <v>1.980998808451642</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -16569,16 +16569,16 @@
       </c>
       <c r="AL44" s="86" t="inlineStr">
         <is>
-          <t>INDERAL LA</t>
+          <t>VALTREX</t>
         </is>
       </c>
       <c r="AM44" s="86" t="inlineStr">
         <is>
-          <t>BETA BLOCKERS &amp; COMBOS</t>
+          <t>HERPES AGENTS</t>
         </is>
       </c>
       <c r="AN44" s="87" t="n">
-        <v>0.9126191751271781</v>
+        <v>5.697071908646854</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" thickBot="1">
@@ -16736,7 +16736,7 @@
         <v>64106.94903390787</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>51.46007802615732</v>
+        <v>51.46007802615733</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -16798,7 +16798,7 @@
         <v>6048.064903563136</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>9.374396464881981</v>
+        <v>9.374396464881979</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -17564,7 +17564,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>904.0980860287003</v>
+        <v>904.0980860287001</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2.294824335148659</v>
@@ -17709,7 +17709,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
@@ -17754,19 +17754,19 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>26.65588284009955</v>
+        <v>26.65588284009954</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>32.74194938540774</v>
+        <v>32.74194938540771</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -17775,13 +17775,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98398526604897</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.10887888966493</v>
+        <v>32.10887888966494</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.557552449006991</v>
@@ -17921,7 +17921,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>47.60579870684875</v>
@@ -18124,14 +18124,14 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
         <v>0</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>0</v>
+        <v>23.38073459894379</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -18183,7 +18183,7 @@
         <v>28.11758592367504</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>284.2684910567109</v>
+        <v>284.2684910567108</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>39.62531155453372</v>
@@ -18205,14 +18205,14 @@
       </c>
       <c r="AF68" s="82" t="inlineStr">
         <is>
-          <t>GLP-1 ANTI-OBESITY AGENTS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AG68" s="125" t="n">
         <v>0</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>23.38073459894379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -19417,7 +19417,7 @@
         <v>13.44783519037637</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>23.9222183650781</v>
+        <v>23.92221836507809</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19942,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
@@ -20241,19 +20241,19 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.03665471204857</v>
+        <v>32.03665471204856</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>38.12272125735676</v>
+        <v>38.12272125735673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -20262,13 +20262,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.89417964245902</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.01907326607498</v>
+        <v>39.019073266075</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>0.557552449006991</v>
@@ -20317,10 +20317,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -20380,7 +20380,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>47.60579870684875</v>
@@ -21655,7 +21655,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>78816.00626191395</v>
+        <v>78816.00626191396</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>61.66266847973219</v>
@@ -21742,16 +21742,16 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>ZEPBOUND</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>0</v>
+        <v>28.05688151873255</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -21809,26 +21809,26 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>6254.51742875308</v>
+        <v>6254.517428753081</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>9.116896294001297</v>
+        <v>9.116896294001295</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>ZEPBOUND</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>GLP-1 ANTI-OBESITY AGENTS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AN27" s="58" t="n">
-        <v>28.05688151873255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" thickTop="1">
@@ -21896,16 +21896,16 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>ACIPHEX</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>0</v>
+        <v>3.909476943476777</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -21973,16 +21973,16 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>LIPITOR</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>STATINS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>0</v>
+        <v>9.213599222747469</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -22050,16 +22050,16 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>JARDIANCE</t>
+          <t>AVODART</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+          <t>PROSTATIC HYPERTROPHY AGENTS</t>
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>0</v>
+        <v>2.024108577352637</v>
       </c>
     </row>
     <row r="31">
@@ -22113,16 +22113,16 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>ACIPHEX</t>
+          <t>SYNTHROID</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>THYROID HORMONES</t>
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>3.909476943476777</v>
+        <v>0</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -22184,16 +22184,16 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>TRELEGY ELLIPTA</t>
+          <t>VIAGRA</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMPOTENCE AGENTS</t>
         </is>
       </c>
       <c r="AN32" s="58" t="n">
-        <v>0</v>
+        <v>9.671273756585533</v>
       </c>
     </row>
     <row r="33">
@@ -22261,12 +22261,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>OZEMPIC</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="AN33" s="58" t="n">
@@ -22338,16 +22338,16 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>LIPITOR</t>
+          <t>NEXIUM</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>STATINS &amp; COMBOS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>9.213599222747469</v>
+        <v>4.886846179345971</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -22415,16 +22415,16 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>AVODART</t>
+          <t>DEXCOM G7 SENSOR</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>PROSTATIC HYPERTROPHY AGENTS</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AN35" s="58" t="n">
-        <v>2.024108577352637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -22492,16 +22492,16 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>SYNTHROID</t>
+          <t>XDEMVY</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>THYROID HORMONES</t>
+          <t>OPHTHALMIC ANTI-INFECTIVES</t>
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>0</v>
+        <v>2.888053564215611</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -22569,16 +22569,16 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>VIAGRA</t>
+          <t>LEXAPRO</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>IMPOTENCE AGENTS</t>
+          <t>ANTIDEPRESSANTS</t>
         </is>
       </c>
       <c r="AN37" s="58" t="n">
-        <v>9.671273756585533</v>
+        <v>3.190511282974973</v>
       </c>
     </row>
     <row r="38" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -22646,16 +22646,16 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>INDERAL LA</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>BETA BLOCKERS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>0</v>
+        <v>0.8874856430441755</v>
       </c>
     </row>
     <row r="39">
@@ -22709,16 +22709,16 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>NEXIUM</t>
+          <t>QNASL</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>NASAL STEROIDS</t>
         </is>
       </c>
       <c r="AN39" s="58" t="n">
-        <v>4.886846179345971</v>
+        <v>4.282746308251838</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -22766,7 +22766,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>543.2691942120091</v>
+        <v>543.269194212009</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>1.577600823760222</v>
@@ -22776,16 +22776,16 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>DEXCOM G7 SENSOR</t>
+          <t>MIEBO</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+          <t>OPHTHALMICS - MISC.</t>
         </is>
       </c>
       <c r="AN40" s="58" t="n">
-        <v>0</v>
+        <v>5.68334448459311</v>
       </c>
     </row>
     <row r="41">
@@ -22853,16 +22853,16 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>XDEMVY</t>
+          <t>COZAAR</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>OPHTHALMIC ANTI-INFECTIVES</t>
+          <t>ANGIOTENSIN II RECEPTOR ANTAGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>2.888053564215611</v>
+        <v>5.96162019316963</v>
       </c>
     </row>
     <row r="42">
@@ -22930,16 +22930,16 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>LEXAPRO</t>
+          <t>CEQUA</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>ANTIDEPRESSANTS</t>
+          <t>OPHTHALMIC IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>3.190511282974973</v>
+        <v>1.965467777793381</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -23007,16 +23007,16 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>INDERAL LA</t>
+          <t>VALTREX</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>BETA BLOCKERS &amp; COMBOS</t>
+          <t>HERPES AGENTS</t>
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>0.8874856430441755</v>
+        <v>5.585751123551895</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -23074,7 +23074,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>63.64211364413745</v>
+        <v>63.64211364413744</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>0.04119416697492106</v>
@@ -23084,16 +23084,16 @@
       </c>
       <c r="AL44" s="86" t="inlineStr">
         <is>
-          <t>QNASL</t>
+          <t>BOTOX</t>
         </is>
       </c>
       <c r="AM44" s="86" t="inlineStr">
         <is>
-          <t>NASAL STEROIDS</t>
+          <t>NEUROMUSCULAR BLOCKING AGENT</t>
         </is>
       </c>
       <c r="AN44" s="87" t="n">
-        <v>4.282746308251838</v>
+        <v>2.948201666690071</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" thickBot="1">
@@ -23248,10 +23248,10 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>78879.6483755581</v>
+        <v>78879.64837555808</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>61.70386264670711</v>
+        <v>61.70386264670712</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23434,7 +23434,7 @@
         <v>6254.517428753081</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>9.284039392724653</v>
+        <v>9.284039392724651</v>
       </c>
     </row>
     <row r="53">
@@ -23900,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -24224,7 +24224,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
@@ -24269,19 +24269,19 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>26.65588284009955</v>
+        <v>26.65588284009954</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>32.74194938540774</v>
+        <v>32.74194938540771</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -24290,13 +24290,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98398526604897</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.10887888966493</v>
+        <v>32.10887888966494</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.557552449006991</v>
@@ -24316,17 +24316,8 @@
       <c r="AE63" s="121" t="n">
         <v>15</v>
       </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>ONCOLOGY</t>
-        </is>
-      </c>
-      <c r="AG63" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG63" s="122" t="n"/>
+      <c r="AH63" s="56" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="64" t="inlineStr">
@@ -24397,8 +24388,17 @@
       <c r="AE64" s="121" t="n">
         <v>16</v>
       </c>
-      <c r="AG64" s="122" t="n"/>
-      <c r="AH64" s="56" t="n"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>ONCOLOGY</t>
+        </is>
+      </c>
+      <c r="AG64" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="98" t="inlineStr">
@@ -24427,7 +24427,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>47.60579870684875</v>
@@ -24558,7 +24558,7 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
@@ -24639,14 +24639,14 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AG67" s="122" t="n">
         <v>0</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>0</v>
+        <v>8.796323122822749</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24698,7 +24698,7 @@
         <v>28.11758592367504</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>284.2684910567109</v>
+        <v>284.2684910567108</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>39.62531155453372</v>
@@ -25924,7 +25924,7 @@
         <v>13.44783519037637</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>23.9222183650781</v>
+        <v>23.92221836507809</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26449,7 +26449,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -26717,7 +26717,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
@@ -26748,19 +26748,19 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.03665471204857</v>
+        <v>32.03665471204856</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>38.12272125735676</v>
+        <v>38.12272125735673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -26769,13 +26769,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.89417964245902</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.01907326607498</v>
+        <v>39.019073266075</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>0.557552449006991</v>
@@ -26824,10 +26824,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -26887,7 +26887,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>47.60579870684875</v>
@@ -28162,10 +28162,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>97701.03174199554</v>
+        <v>97701.03174199552</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>73.90391183428738</v>
+        <v>73.90391183428737</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28249,16 +28249,16 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>ZEPBOUND</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>GLP-1 ANTI-OBESITY AGENTS</t>
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>0</v>
+        <v>33.66825782247906</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -28326,16 +28326,16 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>ZEPBOUND</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>GLP-1 ANTI-OBESITY AGENTS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AN27" s="58" t="n">
-        <v>33.66825782247906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" thickTop="1">
@@ -28403,16 +28403,16 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>ACIPHEX</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>0</v>
+        <v>3.873627039905095</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -28470,7 +28470,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>9.087539887934609</v>
@@ -28480,16 +28480,16 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>LIPITOR</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>STATINS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>0</v>
+        <v>9.219680198234483</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -28557,16 +28557,16 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>JARDIANCE</t>
+          <t>AVODART</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+          <t>PROSTATIC HYPERTROPHY AGENTS</t>
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>0</v>
+        <v>2.021720129231361</v>
       </c>
     </row>
     <row r="31">
@@ -28620,16 +28620,16 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>ACIPHEX</t>
+          <t>VIAGRA</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>IMPOTENCE AGENTS</t>
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>3.873627039905095</v>
+        <v>9.993423885417396</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -28691,12 +28691,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>OZEMPIC</t>
+          <t>SYNTHROID</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>THYROID HORMONES</t>
         </is>
       </c>
       <c r="AN32" s="58" t="n">
@@ -28768,16 +28768,16 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>LIPITOR</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>STATINS &amp; COMBOS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="AN33" s="58" t="n">
-        <v>9.219680198234483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -28845,12 +28845,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>TRELEGY ELLIPTA</t>
+          <t>DEXCOM G7 SENSOR</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
         </is>
       </c>
       <c r="AN34" s="58" t="n">
@@ -28922,16 +28922,16 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>AVODART</t>
+          <t>NEXIUM</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>PROSTATIC HYPERTROPHY AGENTS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AN35" s="58" t="n">
-        <v>2.021720129231361</v>
+        <v>4.842033799881369</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -28989,7 +28989,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>545.4945335050974</v>
+        <v>545.4945335050973</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>1.503942641298857</v>
@@ -28999,16 +28999,16 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>VIAGRA</t>
+          <t>XDEMVY</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>IMPOTENCE AGENTS</t>
+          <t>OPHTHALMIC ANTI-INFECTIVES</t>
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>9.993423885417396</v>
+        <v>3.028701772792912</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -29076,16 +29076,16 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>SYNTHROID</t>
+          <t>LEXAPRO</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>THYROID HORMONES</t>
+          <t>ANTIDEPRESSANTS</t>
         </is>
       </c>
       <c r="AN37" s="58" t="n">
-        <v>0</v>
+        <v>3.22659596558542</v>
       </c>
     </row>
     <row r="38" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -29153,16 +29153,16 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>INDERAL LA</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>BETA BLOCKERS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>0</v>
+        <v>0.8630442884347389</v>
       </c>
     </row>
     <row r="39">
@@ -29216,16 +29216,16 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>DEXCOM G7 SENSOR</t>
+          <t>COZAAR</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+          <t>ANGIOTENSIN II RECEPTOR ANTAGONISTS &amp; COMBOS</t>
         </is>
       </c>
       <c r="AN39" s="58" t="n">
-        <v>0</v>
+        <v>6.120378138913737</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -29283,16 +29283,16 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>NEXIUM</t>
+          <t>QNASL</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>PROTON PUMP INHIBITORS</t>
+          <t>NASAL STEROIDS</t>
         </is>
       </c>
       <c r="AN40" s="58" t="n">
-        <v>4.842033799881369</v>
+        <v>4.08449798164286</v>
       </c>
     </row>
     <row r="41">
@@ -29360,16 +29360,16 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>XDEMVY</t>
+          <t>MIEBO</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>OPHTHALMIC ANTI-INFECTIVES</t>
+          <t>OPHTHALMICS - MISC.</t>
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>3.028701772792912</v>
+        <v>5.160419958565697</v>
       </c>
     </row>
     <row r="42">
@@ -29421,16 +29421,16 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>LEXAPRO</t>
+          <t>CEQUA</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>ANTIDEPRESSANTS</t>
+          <t>OPHTHALMIC IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>3.22659596558542</v>
+        <v>1.950058510415481</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -29482,16 +29482,16 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>INDERAL LA</t>
+          <t>BOTOX</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>BETA BLOCKERS &amp; COMBOS</t>
+          <t>NEUROMUSCULAR BLOCKING AGENT</t>
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>0.8630442884347389</v>
+        <v>2.925087765623221</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -29545,16 +29545,16 @@
       </c>
       <c r="AL44" s="86" t="inlineStr">
         <is>
-          <t>COZAAR</t>
+          <t>VALTREX</t>
         </is>
       </c>
       <c r="AM44" s="86" t="inlineStr">
         <is>
-          <t>ANGIOTENSIN II RECEPTOR ANTAGONISTS &amp; COMBOS</t>
+          <t>HERPES AGENTS</t>
         </is>
       </c>
       <c r="AN44" s="87" t="n">
-        <v>6.120378138913737</v>
+        <v>5.476605546597691</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" thickBot="1">
@@ -30361,7 +30361,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>996.9693816543509</v>
+        <v>996.9693816543506</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>4.511827923896572</v>
@@ -30615,17 +30615,8 @@
       <c r="AE61" s="121" t="n">
         <v>13</v>
       </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>ONCOLOGY</t>
-        </is>
-      </c>
-      <c r="AG61" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG61" s="122" t="n"/>
+      <c r="AH61" s="56" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="64" t="inlineStr">
@@ -30685,7 +30676,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X62" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y62" s="131" t="n">
         <v>0</v>
@@ -30696,8 +30687,17 @@
       <c r="AE62" s="121" t="n">
         <v>14</v>
       </c>
-      <c r="AG62" s="122" t="n"/>
-      <c r="AH62" s="56" t="n"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>ONCOLOGY</t>
+        </is>
+      </c>
+      <c r="AG62" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="64" t="inlineStr">
@@ -30721,19 +30721,19 @@
         <v>35</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>26.65588284009955</v>
+        <v>26.65588284009954</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>32.74194938540774</v>
+        <v>32.74194938540771</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -30742,13 +30742,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>25.98398526604897</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32.10887888966493</v>
+        <v>32.10887888966494</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.557552449006991</v>
@@ -30851,7 +30851,7 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="AG64" s="122" t="n">
@@ -30888,7 +30888,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>47.60579870684875</v>
@@ -30935,17 +30935,8 @@
       <c r="AE65" s="121" t="n">
         <v>17</v>
       </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>HIV-MULTICLASS COMBO</t>
-        </is>
-      </c>
-      <c r="AG65" s="122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" s="56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG65" s="122" t="n"/>
+      <c r="AH65" s="56" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="99" t="n"/>
@@ -31019,14 +31010,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+          <t>PROTON PUMP INHIBITORS</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
         <v>0</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>0.1222914313251853</v>
+        <v>8.715660839786464</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -31098,8 +31089,17 @@
       <c r="AE67" s="121" t="n">
         <v>19</v>
       </c>
-      <c r="AG67" s="122" t="n"/>
-      <c r="AH67" s="56" t="n"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>PROSTATIC HYPERTROPHY AGENTS</t>
+        </is>
+      </c>
+      <c r="AG67" s="122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="56" t="n">
+        <v>9.097740581541125</v>
+      </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
       <c r="B68" s="69" t="inlineStr">
@@ -31150,7 +31150,7 @@
         <v>28.11758592367504</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>284.2684910567109</v>
+        <v>284.2684910567108</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>39.62531155453372</v>
@@ -32376,7 +32376,7 @@
         <v>13.44783519037637</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>23.9222183650781</v>
+        <v>23.92221836507809</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32901,7 +32901,7 @@
         <v>0</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>3.528447109621814</v>
+        <v>3.528447109621815</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -33169,7 +33169,7 @@
         <v>10.58534132886544</v>
       </c>
       <c r="X98" s="131" t="n">
-        <v>53.80881842173266</v>
+        <v>53.80881842173267</v>
       </c>
       <c r="Y98" s="131" t="n">
         <v>0</v>
@@ -33200,19 +33200,19 @@
         <v>35</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6325076527118796</v>
+        <v>0.6325076527118512</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.09887116171637444</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.354687730879931</v>
+        <v>5.354687730879945</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>32.03665471204857</v>
+        <v>32.03665471204856</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>38.12272125735676</v>
+        <v>38.12272125735673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5588274414371597</v>
@@ -33221,13 +33221,13 @@
         <v>0.08086620964898827</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.485199972529813</v>
+        <v>5.485199972529827</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>32.89417964245902</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>39.01907326607498</v>
+        <v>39.019073266075</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>0.557552449006991</v>
@@ -33276,10 +33276,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>27.34398633156188</v>
+        <v>27.34398633156187</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -33339,7 +33339,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>77.89286417713821</v>
+        <v>77.89286417713822</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>47.60579870684875</v>
